--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LK Dây nguồn VNSH03_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LK Dây nguồn VNSH03_240626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1B57A4-D4BB-4591-9EBD-DF12617409F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F7F8DC-94A4-4572-A6D2-8ADD07F13EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -483,6 +483,42 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -497,42 +533,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -935,56 +935,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="34" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="36" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="37"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="38" t="s">
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="34"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="31"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="43"/>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
@@ -1089,14 +1089,14 @@
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32" t="s">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="32"/>
+      <c r="D14" s="44"/>
       <c r="E14" s="24" t="s">
         <v>8</v>
       </c>
@@ -1105,14 +1105,14 @@
       </c>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="33"/>
+      <c r="D15" s="45"/>
       <c r="E15" s="27" t="s">
         <v>3</v>
       </c>
@@ -1161,14 +1161,14 @@
       <c r="F20" s="25"/>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32" t="s">
+      <c r="B21" s="44"/>
+      <c r="C21" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="32"/>
+      <c r="D21" s="44"/>
       <c r="E21" s="24" t="s">
         <v>5</v>
       </c>
@@ -1198,11 +1198,6 @@
   </sheetData>
   <autoFilter ref="A9:F11" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="13">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A1:B4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
@@ -1211,12 +1206,17 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A1:B4"/>
   </mergeCells>
+  <conditionalFormatting sqref="B10:B11">
+    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M1:M9 M12:M1048576 B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LK Dây nguồn VNSH03_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LK Dây nguồn VNSH03_240626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F7F8DC-94A4-4572-A6D2-8ADD07F13EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027BFD29-EC98-4278-A53A-EE82A355040B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -483,6 +483,27 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -517,27 +538,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -935,56 +935,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="37"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="31" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="33" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="34"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="41"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="43"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
@@ -1051,7 +1051,7 @@
       <c r="D10" s="28">
         <v>750</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="34" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="20"/>
@@ -1069,7 +1069,7 @@
       <c r="D11" s="28">
         <v>500</v>
       </c>
-      <c r="E11" s="47"/>
+      <c r="E11" s="35"/>
       <c r="F11" s="20"/>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1089,14 +1089,14 @@
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44" t="s">
+      <c r="B14" s="32"/>
+      <c r="C14" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="44"/>
+      <c r="D14" s="32"/>
       <c r="E14" s="24" t="s">
         <v>8</v>
       </c>
@@ -1105,14 +1105,14 @@
       </c>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="45"/>
+      <c r="D15" s="33"/>
       <c r="E15" s="27" t="s">
         <v>3</v>
       </c>
@@ -1161,14 +1161,14 @@
       <c r="F20" s="25"/>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44" t="s">
+      <c r="B21" s="32"/>
+      <c r="C21" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="44"/>
+      <c r="D21" s="32"/>
       <c r="E21" s="24" t="s">
         <v>5</v>
       </c>
@@ -1198,6 +1198,11 @@
   </sheetData>
   <autoFilter ref="A9:F11" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="13">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A1:B4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
@@ -1206,11 +1211,6 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A1:B4"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:B11">
     <cfRule type="duplicateValues" dxfId="1" priority="53"/>
